--- a/data/araclar.xlsx
+++ b/data/araclar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahip\Documents\olcme_araclari_rehberi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F29DD33-BC10-43F0-98B9-A6B6A53FCBAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BF9853-C40F-46F2-A511-B661A99ECD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/data/araclar.xlsx
+++ b/data/araclar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahip\Documents\olcme_araclari_rehberi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BF9853-C40F-46F2-A511-B661A99ECD09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4801459D-72D9-4ECE-AB65-593E29C75F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
   <si>
     <t>arac_id</t>
   </si>
@@ -55,13 +55,7 @@
     <t>Ölçme ve Değerlendirme Araçları</t>
   </si>
   <si>
-    <t>Açık uçlu sorular</t>
-  </si>
-  <si>
     <t>...</t>
-  </si>
-  <si>
-    <t>Ağaç şeması</t>
   </si>
   <si>
     <t>Zihin haritası</t>
@@ -206,12 +200,377 @@
     <t>DKAB.5.2.2. Namazın kılınışını gözlemleyebilme
 *c) Namazın kılınışı hakkında topladığı bilgileri sınıflandırır ve kaydeder.</t>
   </si>
+  <si>
+    <t>Açık Uçlu Sorular</t>
+  </si>
+  <si>
+    <t>Ağaç Şeması</t>
+  </si>
+  <si>
+    <t>ornek3_cikti</t>
+  </si>
+  <si>
+    <t>TDB.1.1.2. İlkeli yaşamanın önemini idrak edebilme
+*a) İlkeli yaşamanın önemiyle ilgili tefekkür sürecini gözden geçirir.
+*b) İlkeli yaşamanın önemiyle ilgili tefekkür sürecine dayalı çıkarım yapar.</t>
+  </si>
+  <si>
+    <t>AKD.11.2.1. Allah’ın (cc) varlığı ve birliğine ilişkin akli ve naklî delilleri kullanabilme
+*b) Allah’ın (cc) varlığı ve birliğine ilişkin topladığı deliller arasında ilişki kurar.
+*c) Allah’ın (cc) varlığı ve birliğiyle ilgili bir konuyu seçtiği akli veya naklî delile dayandırarak
+değerlendirir.
+*ç) İlişki kurduğu akli veya naklî delile ilgili konuda amaca uygun şekilde yer verir.</t>
+  </si>
+  <si>
+    <t>Anlam çözümleme tablosu</t>
+  </si>
+  <si>
+    <t>Anlamsal çağrışım haritası</t>
+  </si>
+  <si>
+    <t>Bağlam temelli sorular</t>
+  </si>
+  <si>
+    <t>Balık kılçığı</t>
+  </si>
+  <si>
+    <t>Bilgi görseli</t>
+  </si>
+  <si>
+    <t>Bilgi haritası</t>
+  </si>
+  <si>
+    <t>Boşluk doldurma soruları</t>
+  </si>
+  <si>
+    <t>Bulmacalar</t>
+  </si>
+  <si>
+    <t>Bülten panosu</t>
+  </si>
+  <si>
+    <t>Çoklu seçim soruları</t>
+  </si>
+  <si>
+    <t>Çoktan seçmeli sorular</t>
+  </si>
+  <si>
+    <t>Doğru yanlış soruları</t>
+  </si>
+  <si>
+    <t>Eşleştirme soruları</t>
+  </si>
+  <si>
+    <t>Frayer modeli (Kavram analizi şeması)</t>
+  </si>
+  <si>
+    <t>Giriş-çıkış kartları</t>
+  </si>
+  <si>
+    <t>İki aşamalı testler</t>
+  </si>
+  <si>
+    <t>Karşılaştırma tablosu</t>
+  </si>
+  <si>
+    <t>Kavram haritası</t>
+  </si>
+  <si>
+    <t>Kavram karikatürü</t>
+  </si>
+  <si>
+    <t>Kelime ilişkilendirme testi</t>
+  </si>
+  <si>
+    <t>Kısa cevaplı sorular</t>
+  </si>
+  <si>
+    <t>Kümeleme (Cluster)</t>
+  </si>
+  <si>
+    <t>Organizasyon şeması</t>
+  </si>
+  <si>
+    <t>Öğrenme duvarı</t>
+  </si>
+  <si>
+    <t>Öğrenme günlüğü</t>
+  </si>
+  <si>
+    <t>Performans görevleri</t>
+  </si>
+  <si>
+    <t>Portfolyo – elektronik portfolyo</t>
+  </si>
+  <si>
+    <t>Tanılayıcı dallanmış ağaç</t>
+  </si>
+  <si>
+    <t>Tarsia yapboz</t>
+  </si>
+  <si>
+    <t>T-tablosu</t>
+  </si>
+  <si>
+    <t>Üçgen-Kare-Çember</t>
+  </si>
+  <si>
+    <t>Venn şeması</t>
+  </si>
+  <si>
+    <t>Yansıtıcı yazı</t>
+  </si>
+  <si>
+    <t>Yapılandırılmış grid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Konu/kavramlara ilişkin özelliklerin belirlenerek kavramlar arasındaki benzerlik ve farklılıkların ortaya çıkarılması için kullanılan etkinlik veya değerlendirme aracıdır. Anlam çözümleme tabloları öğrencilerin sistematik düşünmelerini ve kavramları ilişkilendirmelerini sağlar. Anlam çözümleme tabloları iki boyutlu olarak hazırlanır. Tablonun bir boyutunda özellikleri çözümlenecek konu/kavramlar, diğer boyutunda konu/kavramların özellikleri sıralanır. Öğrencilerden, ilk boyutta verilen konu/kavramlar ile ikinci boyutta verilen özellikler/sınıflandırmalar arasında ilişki kurmaları ve yönergede belirtilen şekilde işaretleme yaparak tabloyu doldurmaları istenir.
+</t>
+  </si>
+  <si>
+    <t>*Ölçme aracı doğrudan ilgili öğrenme çıktısı veya süreç bileşenini ölçmelidir.
+*Seçilen kavramlar aynı kategoriye ait ve birbirleriyle karşılaştırılabilir nitelikte olmalıdır.
+*Özellikler ayırt edici, gözlenebilir ve nesnel olmalıdır; subjektif ve genelleyici ifadelerden kaçınılmalıdır.
+*Her özellik bazı kavramlar için geçerli, bazıları için geçersiz olacak şekilde düzenlenmelidir.
+*Tablo yapısı sistematik olmalıdır. Sütunlarda kavramlar, satırlarda özellikler yer almalıdır.
+*İşaretleme biçimi (✔/✘, +/– vb.) açık ve tutarlı kullanılmalıdır.
+*Yönerge ve tablodaki özellikler açık, anlaşılır ve öğrenci düzeyine uygun yazılmalıdır.
+*Tablo, ezberi değil kavramsal ayırt etme ve ilişkilendirme becerisini ölçmeye hizmet etmelidir.
+*Tablo öğrenme çıktısının içeriğini yeterli düzeyde temsil etmelidir.
+*Tekrarlayan ve birbirini kapsayan özelliklerden kaçınılmalıdır.</t>
+  </si>
+  <si>
+    <t>KB2.4. Çözümleme Becerisi
+KB2.5. Sınıflandırma Becerisi
+KB2.7. Karşılaştırma Becerisi
+DAB3.1. Dinî Kavramları Ayırt Etme
+DAB3.2.SB3. Dinî kavramların benzerliklerini ve farklılıklarını açıklamak
+DAB4.3.SB2.Görüşleri/argümanları karşılaştırmak
+DAB5.2. SB2. Belirlenen özelliklere ilişkin benzerlikleri ortaya koymak
+DAB5.2.SB3. Belirlenen özelliklere ilişkin farklılıkları ortaya koymak</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PH.9.3.2. Akabe biatlerini karşılaştırabilme
+*b) Birinci ve İkinci Akabe biatleri ile ilgili öğrendiği özelliklere ilişkin benzerlikleri listeler.
+*c) Birinci ve İkinci Akabe biatleri ile ilgili öğrendiği özelliklere ilişkin farklılıkları listeler.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH.9.3.4. Hicret’ten sonra devletleşme sürecinde gerçekleşen faaliyetleri sınıflandırabilme
+*c) Medine’de devletleşme sürecinde gerçekleşen faaliyetleri tasnif eder. 
+*ç) Medine’de devletleşme sürecinde gerçekleşen faaliyetlere dair tasnifi isimlendirir.  </t>
+  </si>
+  <si>
+    <t>Verilen bir kavramla ilgili zihinde çağrışım yapan kelime veya kavramları görselleştiren bir şema türüdür. Bu yöntemin temeli, bir bilginin veya düşüncenin anlamca ilişkili olduğu başka bir bilgiyi hatırlatmasına dayanır. Öğrencinin önceki bilgi ve deneyimleri ne kadar zengin olursa, kurduğu bağlantılar ve hatırlama düzeyi de o kadar artar. Kavramlar arasında benzerlik, zıtlık ve ilişkisel çağrışımlar kurularak öğrencinin dikkati çekilir ve öğrenme süreci daha anlamlı hâle gelir. Kavramlara yönelik öğrencilerin ön öğrenmelerini tespit etmek veya süreç değerlendirme yapmak amacıyla kullanılır.</t>
+  </si>
+  <si>
+    <t>*Harita oluşturulmadan önce öğretim programındaki hangi anahtar kavram/içerik/konuya odaklanılacağı netleştirilmelidir.
+*Haritanın görsel olarak etkili bir şekilde sunulabileceği bir yapı oluşturulmalıdır. Bu yapıda ana kavram merkezde yer almalı ve öğrenciden bu kavramın zihninde uyandırdığı/çağrıştırdığı diğer kavramları eklemesi istenmelidir.</t>
+  </si>
+  <si>
+    <t>KB2.13.SB1. Mevcut olayı/konuyu/durumu inceleyerek hiyerarşik, nedensel ya da mantıksal ilişkiler ortaya koymak. 
+KB2.4. Çözümleme Becerisi
+KB2.20.SB1. Parçaları belirlemek
+KB2.15.SB1. Deneyimi gözden geçirmek
+DAB3.1. Dinî Kavramları Ayırt Etme (SB1)
+DAB3.2. Dinî Kavramları Bağlamına Uygun Kullanma (SB2, SB3)
+DAB4.2.Dinî Meseleleri Anlama (SB1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TDB.9.3.1. İbadet ile ilgili kavramları ayırt edebilme 
+*a) İbadet ile ilgili kavramları tespit eder. </t>
+  </si>
+  <si>
+    <t>Ön Değerlendirme: Öğrencilerden şükür ve hamt kelimeleriyle ilgili anlam çağrışım haritası oluşturmaları istenebilir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akran değerlendirme, öğrencilerin sınıf arkadaşlarının çalışmalarını belirli ölçütlere göre değerlendirmesiyle gerçekleşir. İki şekilde yapılır: I) Her bir öğrenci başka bir öğrencinin çalışmasını değerlendirir; II) Bir öğrencinin çalışması sınıftaki tüm öğrenciler tarafından değerlendirilir. Akran değerlendirme formu açık uçlu sorularla oluşturulabileceği gibi, dereceleme ölçeği veya kontrol listesi şeklinde de hazırlanabilir. Akran değerlendirme, hem öğrencilerin grup içindeki bireysel çabalarını ortaya koyma hem de gruba katkısını değerlendirmede etkili bir araçtır.
+Akran değerlendirmede, öğrenci arkadaşının hazırladığı ödevi/ürünü değerlendirirken yanlı davranabilir bu da değerlendirmede geçerliği etkileyebilir. Öğrenci arkadaşını değerlendirirken tam anlamıyla tarafsız olmayabilir. Bu açıdan akran değerlendirme formlarının yönergeleri dikkatli hazırlanmalıdır.
+</t>
+  </si>
+  <si>
+    <t>*Öğrenciler, formu doldurmaya başlamadan önce bu değerlendirmenin neden yapıldığı konusunda bilgilendirilmelidir. 
+*Öğrenci, arkadaşını değerlendirirken tarafsız ve adil olması, eleştirilerini ise nezaket ve saygı çerçevesinde sunması konusunda form aracılığıyla yönlendirilmelidir.
+*Değerlendirme ölçütleri öğrencilerin seviyesine uygun, sade ve net bir dille yazılmalıdır.
+*Öğrencinin "neye bakacağını" tam olarak bilmesi sağlanmalıdır. "Arkadaşım görevini yaptı" yerine "Arkadaşım grup çalışmasında üzerine düşen sorumluluğu zamanında yerine getirdi" gibi somut ifadeler kullanılmalıdır.
+*Öğrencilerin birbirlerine yapıcı geri bildirim verebileceği açık uçlu bölümler (Örn: “Arkadaşımın çalışmasında en çok beğendiğim yön...”, “Arkadaşım şu noktayı geliştirirse daha iyi olur...”) kullanılabilir.
+*TYMM'nin “Yetkin ve Erdemli İnsan” profilinde yer alan saygı, adalet, dürüstlük ve yardımseverlik gibi değerler akran değerlendirme sürecine dahil edilebilir.
+*Özellikle grup çalışmaları için hazırlanan akran değerlendirme formlarında; SDB2.2. İş Birliği ve SDB2.1. Öz Düzenleme becerilerine yönelik maddeler (Örn: “Grup içindeki farklı düşünceler üzerinde uzlaşmak için çözüm aradı”, “Diğerlerinin fikirlerini dikkatle dinledi”) bulunmalıdır.</t>
+  </si>
+  <si>
+    <t>KB2.18.SB1. Mantıksal temellendirme yapmak (Tartışma becerisi)
+KB2.18.SB2. Mantıksal çelişkileri ve/veya tutarsızlıkları tespit etmek (Tartışma becerisi)
+SDB2.1.SB1. Başkalarını etkin şekilde dinlemek (İletişim becerisi)
+SDB2.1.SB2. Duygu ve düşünceleri ifade etmek (İletişim becerisi)
+SDB2.2.SB1. Kişi ve gruplarla iş birliği yapmak (İş birliği becerisi)
+SDB2.2.SB2. Düşüncelerini başkalarıyla tartışmak/müzakere etmek (İş birliği becerisi)
+SDB2.2.SB4. Ekip (takım) çalışması yapmak ve yardımlaşmak (İş birliği becerisi)
+SDB2.3. Sosyal Farkındalık Becerisi: Başkalarının bakış açılarını anlama ve onlarla hemhâl olmayı ifade eder.
+SDB2.3.SB2. Başkalarının duygularını, düşüncelerini ve bakış açılarını anlamak (Sosyal farkındalık becerisi)
+SDB2.3. SB3. Başkalarına karşı anlayış geliştirerek saygı göstermek (Sosyal farkındalık becerisi)
+SDB3.2.SB2. Farklı fikir ve önerilere açık olmak: Akranından gelen eleştiri ve önerileri savunmacı bir tutum takınmadan dinlemek (Esneklik becerisi)
+SDB3.2.SB3. Yeni durumlara göre davranışlarını uyarlamak: Aldığı geri bildirimler doğrultusunda kendi çalışmasını/performansını iyileştirmeye yönelik adım atmak (Esneklik becerisi)
+SDB3.3. Sorumlu Karar Verme Becerisi
+DAB8.1.SB4. Hitabet türü ile ilgili uygulama süreçlerini değerlendirmek (Hitabet ve Mesleki Uygulama)
+DAB8.2.SB4. Mesleki uygulama süreçlerini değerlendirmek (Hitabet ve Mesleki Uygulama)
+DAB7.1.SB4. Harfleri/harekeleri/işaretleri doğru bir şekilde telaffuz etmek (Gözlem yoluyla akran onayı) (Tilavet Becerisi)
+DAB4.4.SB3. Akıl yürütme ile ulaştığı çıkarımları tartışmak (Grup içi akran müzakeresi) (Tefekkür Becerisi)</t>
+  </si>
+  <si>
+    <t>Öğretim programındaki ifade: “... Öğrencilerden İslam öncesinde Mekke’de yaşadığı varsayılan bir kişiyle yapılmış bir söyleşiyi drama tekniği kullanarak kurgulamaları istenebilir. Yapılan çalışma öz ve akran değerlendirme formları kullanılarak değerlendirilebilir.”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bağlam temelli sorular; bilgiyi ezber düzeyinde ölçmek yerine, bu bilginin gerçek hayattaki bir durum veya senaryo içerisinde nasıl kullanıldığını test eden sorulardır. Bu soru tipinin en temel özelliği, bilginin transfer edilebilirliğini ölçmesidir. Öğrenci, derste öğrendiği teorik bir kavramı, soruda sunulan günlük yaşam durumu ile ilişkilendirerek sonuca ulaşır. Bağlam temelli olma durumu, sorunun formatından çok nasıl bir bağlam içinde kurgulandığı ve öğrenciden ne tür bir bilişsel işlem talep ettiği ile ilgilidir. Bağlam temelli bir soru; öğrencinin metin, problem durumu, veri seti, görsel ya da senaryo gibi anlamlı bir bağlamla karşılaşmasını ve bu bağlamı kullanarak karar vermesini, yorum yapmasını, çözüm üretmesini ya da açıklama getirmesini gerektirir. Bağlam temelli sorular, bir soru tipi olmaktan ziyade bir tasarım yaklaşımıdır ve çoktan seçmeli, uzun yanıtlı, doğru-yanlış, eşleştirme veya kısa yanıtlı olabilir.
+Bağlam temelli sorularla ilgili daha ayrıntılı bilgilere ulaşmak için tıklayınız.
+</t>
+  </si>
+  <si>
+    <t>*Öğrenci soruyu, bağlamı (metin, görsel vb.) incelemeden, hatırladığı bilgileri kullanarak çözebiliyorsa o bağlam işlevsiz kabul edilip yeniden kurgulanmalıdır.
+*Kurgulanan senaryolar gerçek yaşam durumlarını yansıtmalıdır. Bir bakıma bağlamlar öğrenilen bilgi ve becerilen günlük yaşamdaki karşılıklarını içermelidir. 
+*Kullanılan dil yapısı, cümle uzunluğu, terminoloji ve sayısal veriler öğrencilerin sınıf düzeyine uygun olmalıdır. 
+*Hazırbulunuşluk düzeyini aşan kavramlar kullanılmamalıdır.
+*İlgisiz detaylar ve yalnızca dekoratif amaçla eklenmiş görseller öğrencinin işleyen belleğini yoracağından bunlardan kaçınılmalıdır.
+*Anlatım bozukluğu içeren veya birden fazla anlama gelebilecek ifadeler düzeltilmeli; metin ile görsel arasındaki bütünlük, dikkat dağıtmayacak şekilde tasarlanmalıdır.
+*Soru kökü, ölçülmesi hedeflenen öğrenme çıktısındaki süreç bileşenini doğrudan harekete geçirecek ifadeler içermelidir.
+*"Sizce" gibi puanlama güvenirliğini düşüren öznel ifadeler yerine, metne dayalı nesnel ifadeler tercih edilmelidir.
+*Bir bağlamdan bir veya birden fazla soru üretilebilir. Eğer aynı bağlam üzerinden birden fazla soru soruluyorsa, bir sorunun yanıtı diğerinin ön koşulu olmamalı ve sorular arasında birbirine ipucu verecek zincirleme kurgulara yer verilmemelidir.
+*Çeldiriciler rastgele veya bariz yanlışlardan değil öğrencilerin konuyu eksik öğrenmesi veya yanlış akıl yürütmesi nedeniyle düşebilecekleri bilimsel kavram yanılgılarından seçilmelidir.
+*Seçeneklerde metindeki cümleler birebir kullanılmamalı, öğrencinin yorumlama becerisini ölçmek için anlamca özdeş farklı ifadeler tercih edilmelidir.
+*Soruda kullanılan grafik veya görseller metinde yazılanları tekrar etmek yerine, sorunun çözümü için gerekli olan yeni bir bilgiyi sunmalıdır.
+*Bilişsel odaklanmayı artırmak ve okuma kolaylığı sağlamak adına bağlam ile ona ait sorular aynı görsel alanda (aynı sayfada) bulunmalıdır.</t>
+  </si>
+  <si>
+    <t>KB3.3.SB1. Olayı/konuyu/problemi veya durumu sorgulamak (Eleştirel düşünme becerisi)
+KB3.3.SB2. Sorgulanan olay/konu/problem veya durum ile ilgili akıl yürütmek (Eleştirel düşünme becerisi)
+KB3.2.SB1. Problemi yapılandırmak (Problem çözme becerisi)
+KB3.2.SB4. Problemin çözümüne yönelik önermeler üzerinden akıl yürütmek (Problem çözme becerisi)
+KB2.14.SB2. Mevcut olayı/konuyu/durumu bağlamdan kopmadan dönüştürmek
+KB2.14.SB3. Kendi ifadeleriyle olayı/konuyu/durumu nesnel, doğru ve anlamı değiştirmeyecek şekilde yeniden ifade etmek (Yorumlama becerisi)
+KB2.3. Özetleme becerisi
+KB2.4. Çözümleme becerisi
+KB2.7. Karşılaştırma becerisi
+KB2.8. Sorgulama becerisi
+KB2.9. Genelleme becerisi
+KB2.10. Çıkarım yapma becerisi
+KB2.13. Yapılandırma becerisi
+KB2.16.3. Analojik Akıl Yürütme Becerisi
+DAB1.1. Kur’an-ı Kerim Meallerine Başvurma
+DAB1.2. Hadis Kaynaklarına Başvurma
+DAB2.1.SB3. Seçilen dinî kaynaklardan olay/konu/durum ile ilgili bilgileri bulmak
+DAB2.1.SB4. Ulaşılan bilgiler ışığında seçtiği dinî kaynakları karşılaştırmak
+DAB2.1.SB5. Ulaşılan bilgiler ışığında seçtiği dinî kaynakları değerlendirmek
+DAB2.2. Dinî Kaynakların İlişkisini Değerlendirme
+DAB3.2. Dinî Kavramları Bağlamına Uygun Kullanma 
+DAB3.3. Dinî Metinleri Yorumlama DAB3.4. Dinî Metinleri Tahlil Etme
+DAB4.1. Müşahede Etme 
+DAB4.2. Dinî Meseleleri Anlama 
+DAB4.3. Dinî Görüşleri/Argümanları İrdeleme 
+DAB4.4. Dinî Konularda Analitik Düşünme</t>
+  </si>
+  <si>
+    <t>DKAB.9.1.4. Rum suresinin 17-27. ayetlerinin mesajlarını anlamada temel kaynakları
+kullanabilme
+*a) Rum suresinin 17-27. ayetlerinin mesajlarını anlamada Kur’an-ı Kerim meallerine başvurur.
+*b) Rum suresinin 17-27. ayetlerinin mesajlarını anlamada hadis kaynaklarına başvurur.</t>
+  </si>
+  <si>
+    <t>DKAB.9.2.2. İslam’ın iman esaslarını ayet ve hadisler bağlamında özetleyebilme
+*a) Ayet ve hadislerden hareketle İslam’ın iman esaslarına ilişkin çözümleme yapar.</t>
+  </si>
+  <si>
+    <t>İlk defa Kaoru Ishikawa tarafından kullanılan balık kılçığı diyagramı, belirli bir problemi doğuran veya etkileyen sebep veya faktörleri göstermek amacıyla kullanılan bir grafik düzenleyicidir. Bu teknik, sorunu ortaya çıkaran ana nedenlerin ve bu nedenlere katkı sağlayan ikincil alt etkenlerin tek bir şema üzerinde organize bir şekilde gösterilmesini sağlar. Problem çözme sürecini daha düzenli hâle getiren bu diyagram, problemin tüm yönleriyle derinlemesine ve objektif bir şekilde incelenmesine de olanak tanır.</t>
+  </si>
+  <si>
+    <t>*Analiz edilecek problem/durum/olay net bir şekilde belirlenmelidir.
+*Sayfanın ortasına soldan sağa doğru bir ana kılçık çizilmeli ve sağ taraftaki uç kısma (baş kısmına) sonuç/durum/problem bir kutu içinde yazılmalıdır.
+*Ana kılçık üzerine çizilecek küçük alt kılçıklar için üstten veya alttan başlanarak sola doğru ilerlenebilir ve ihtiyaç duyulduğu kadar küçük kılçık eklenebilir.
+*Seçilen problemin/konunun/olayın balık kılçığı tekniğine uyarlanabilir özellikler taşımasına (sebep-sonuç, neden-sonuç, amaç-sonuç ilişkisi taşıması) dikkat edilmelidir.</t>
+  </si>
+  <si>
+    <t>KB2.4.Çözümleme Becerisi
+KB2.5.Sınıflandırma Becerisi
+KB2.16.Muhakeme (Akıl Yürütme) Becerisi
+KB2.13.SB1. Mevcut olayı/konuyu/durumu inceleyerek hiyerarşik, nedensel ya da mantıksal ilişkiler ortaya koymak. (Yapılandırma becerisi)
+DAB4.2. Dinî Meseleleri Anlama
+DAB4.4. Dinî Konularda Analitik Düşünme
+DAB5.1. Akli/Naklî Delilleri Kullanma
+DAB3.4. Dinî Metinleri Tahlil Etme</t>
+  </si>
+  <si>
+    <t>DKAB.7.3.1. Din anlayışındaki yorum farklılıklarının sebeplerini anlayabilme
+*c) Din anlayışındaki yorum farklılıklarının ortaya çıkış sebeplerini açıklar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgi görselleri; tablo, kavram haritası, şema, grafik gibi farklı formatlarda hazırlanabilir. Ölçme ve değerlendirme amacıyla kullanılan bilgi görselinin devamında bir ya da birkaç soru sorulması gerekir. Bu durumda bilgi görseli öncül ya da bağlam işlevi görür. Bu tür görseller aracılığıyla öğrencilerin yalnızca ezberledikleri bilgileri aktarmaları değil bilgileri analiz etme, karşılaştırma, sınıflandırma ve ilişkilendirme becerileri de ölçülebilmektedir. </t>
+  </si>
+  <si>
+    <t>*Görseller açık, anlaşılır ve amaca uygun şekilde hazırlanmalıdır.
+*Görseller öğrencilerin yaş ve gelişim düzeyine uygun olmalıdır.
+*Öğrenme çıktıları ile doğrudan ilişkili olmalıdır.
+*Tablo, kavram haritası, şema, grafik gibi farklı formatlarda hazırlanabilir.
+*Örnek soru kalıpları:
+**Bu bilgi görselinden aşağıdaki çıkarımlardan hangilerine ulaşılabilir / ulaşılamaz?
+**Bu bilgi görselinde boş bırakılan yerleri, verilen kavramlardan uygun olanlarla tamamlayınız.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KB2.4. Çözümleme Becerisi 
+KB2.14.SB3. Kendi ifadeleriyle olayı/konuyu/durumu nesnel, doğru ve anlamı değiştirmeyecek şekilde yeniden ifade etmek.  
+KB2.13.SB1. Mevcut olayı/konuyu/durumu inceleyerek hiyerarşik, nedensel ya da mantıksal ilişkiler ortaya koymak.  
+KB2.10.SB1. Mevcut bilgisi dâhilinde varsayımda bulunmak
+KB2.10.SB3. Kanıta dayalı çıkarım yapmak
+KB2.18.SB1. Mevcut verileri/durumu incelemek
+KB2.18.SB2. Veriler/durumlar arasındaki ilişki örüntülerini belirlemek.
+KB2.7.SB2. Belirlenen özelliklere ilişkin benzerlikleri listelemek.  
+KB2.7.SB3. Belirlenen özelliklere ilişkin farklılıkları listelemek.  
+DAB3.2.SB3. Dinî kavramların benzerliklerini ve farklılıklarını açıklamak.  
+DAB4.4.SB1. Dinî olgular/olaylar/konular/kavramlar/meseleler arasında ilişki kurmak.  
+DAB5.2.SB5. Ortaya konulan benzerlik ve farklılıklara dayalı olarak çıkarım yapmak.  </t>
+  </si>
+  <si>
+    <t>PH.9.2.2. Hz. Hatice’nin, Hz. Peygamber’in hayatındaki yeri hakkında sentezleme yapabilme
+*a) Hz. Hatice’nin, Hz. Peygamber’in hayatındaki yerine dair bilgileri araştırır.
+*b) Hz. Hatice’nin, Hz. Peygamber’in hayatındaki yerine dair öğrendiği bilgiler arasında ilişki kurar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bilgi haritası, bir metinde yer alan önemli bilgilerle bu bilgiler arasındaki bağlantıları görsel bir şema ile sunan iki boyutlu bir yapılandırma tekniğidir. Bu teknikte, metinde geçen ana kavramlara ait tanımlar, özellikler, örnekler ve özet niteliğindeki bilgiler şematik kutucuklar içerisinde gösterilir. Önemli oranda bilgiyi düzenli bir biçimde sunan bilgi haritaları, konunun genel bir özetinin çıkarılmasına ve önemli bilgiler ile önemsiz olanların birbirinden ayırt edilmesine olanak tanır. Akış şemaları ve diyagramlara benzeyen yapısıyla öğrencilerin sadece anlama becerilerini değil sorun çözme ve karar verme yeteneklerini de geliştirir. Ancak, bilgi haritaları hiyerarşik ilişkilerin, sıralı süreçlerin ve diğer karmaşık ilişkilerin açıklanmasında daha geniş bir esnekliğe sahiptir. Kavram haritaları veya kavram ağlarında şemanın üzerinde doğrudan cümle yazılmazken bilgi haritalarında yazılabilir. </t>
+  </si>
+  <si>
+    <t>*Konuyu en iyi şekilde ifade eden temel kavram, sayfanın en üstünde veya ortasında bir çerçeve içerisinde yer almalıdır.
+*Ana konuyu daha az ifade eden alt kavramlar belirlenmeli ve bunlar temel kavramın altına (veya çevresine) yazılmalıdır.
+*Temel kavram ile alt kavramların sahip oldukları tüm özellikler de yine çerçeve içine alınarak yazılmalıdır.
+*Temel kavram, alt kavramlar ve bunlara ait özellikler arasındaki bağlantılar, oklar kullanılarak çerçeve içerisinde net bir şekilde gösterilmelidir.</t>
+  </si>
+  <si>
+    <t>KB2.4. Çözümleme Becerisi
+KB2.13. Yapılandırma Becerisi
+KB2.5. Sınıflandırma Becerisi
+KB2.3. Özetleme Becerisi
+KB2.6. Bilgi Toplama Becerisi
+KB2.16.2.SB2. Olay/konu/durum arasında bütün-bütün veya bütün-parça ilişkisi kurmak
+DAB3.1. Dinî Kavramları Ayırt Etme
+DAB3.2. Dinî Kavramları Bağlamına Uygun Kullanma
+DAB4.1.SB3. Merak ettiği olgu/olay/konu/kavram/meseleleri incelemek
+DAB4.4.SB1. Dinî olgu/olay/konu/kavram/meseleler arasında ilişki kurmak
+DAB5.1.SB1. Olgu/olay/konu/kavram/meselelerle ilgili akli/nakli delilleri toplamak
+DAB5.1.SB2. Olgu/olay/konu/kavram/meselelerle ilgili topladığı akli/nakli deliller arasında ilişki kurmak</t>
+  </si>
+  <si>
+    <t>TZHP.I.1.4. Renkleri özelliklerine göre sınıflandırabilme
+*a) Renklerin özelliklerini inceler.
+*b) Renkleri özelliklerine göre ayrıştırır.
+*c) Renkleri özelliklerine göre gruplandırır.
+*ç) Renkleri özelliklerine göre etiketlendirir.</t>
+  </si>
+  <si>
+    <t>SYR.10.3.2. Hz. Peygamber’in farklı inanç gruplarıyla ilişkilerini değerlendirebilme
+*ç) Hz. Peygamber’in farklı inanç gruplarıyla ilişkilerine dair yaptığı karşılaştırmalar hakkında yargıda bulunur.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,6 +585,14 @@
       <family val="2"/>
       <charset val="162"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="162"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -235,7 +602,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -258,11 +625,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -274,6 +650,15 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -556,17 +941,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="2" max="2" width="14.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
     <col min="4" max="4" width="38.6640625" customWidth="1"/>
     <col min="5" max="5" width="71.44140625" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="32.5546875" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="26.77734375" customWidth="1"/>
+    <col min="9" max="9" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -591,8 +979,11 @@
       <c r="H1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="246.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="I1" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="246.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -600,22 +991,28 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
+        <v>33</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -623,25 +1020,25 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="344.4" thickBot="1" x14ac:dyDescent="0.35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="344.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -649,348 +1046,514 @@
         <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="252" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="1:8" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C8" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="357.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>49</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>50</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>51</v>
+      </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>52</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>53</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>54</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>55</v>
+      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>56</v>
+      </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
+      <c r="B19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
+      <c r="B20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>58</v>
+      </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>59</v>
+      </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>60</v>
+      </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
+      <c r="B23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>61</v>
+      </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
     </row>
-    <row r="24" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>62</v>
+      </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>24</v>
       </c>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>64</v>
+      </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>26</v>
       </c>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>65</v>
+      </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>66</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28</v>
       </c>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>67</v>
+      </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>68</v>
+      </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>30</v>
       </c>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>69</v>
+      </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>32</v>
       </c>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>71</v>
+      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
@@ -1000,101 +1563,121 @@
       <c r="A34" s="3">
         <v>33</v>
       </c>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>72</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
+      <c r="B35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>73</v>
+      </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
+      <c r="B36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>74</v>
+      </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>37</v>
       </c>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
+      <c r="B38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>76</v>
+      </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>12</v>
+      <c r="B39" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
@@ -1102,22 +1685,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="D41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
@@ -1125,45 +1708,45 @@
         <v>41</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>10</v>
+        <v>88</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>10</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
@@ -1171,22 +1754,22 @@
         <v>43</v>
       </c>
       <c r="B44" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="D44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
@@ -1194,22 +1777,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
@@ -1217,22 +1800,22 @@
         <v>45</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
@@ -1240,22 +1823,22 @@
         <v>46</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
@@ -1263,22 +1846,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C48" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="D48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/araclar.xlsx
+++ b/data/araclar.xlsx
@@ -638,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -652,14 +652,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -954,7 +951,7 @@
     <col min="9" max="9" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1112,7 +1109,7 @@
       <c r="G6" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="4" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1229,7 +1226,7 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1244,7 +1241,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1259,7 +1256,7 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1289,7 +1286,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -1304,7 +1301,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1319,7 +1316,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1334,7 +1331,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -1349,7 +1346,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3">
         <v>19</v>
       </c>
@@ -1364,7 +1361,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3">
         <v>20</v>
       </c>
@@ -1379,7 +1376,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3">
         <v>21</v>
       </c>
@@ -1394,7 +1391,7 @@
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
     </row>
-    <row r="23" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3">
         <v>22</v>
       </c>
@@ -1424,7 +1421,7 @@
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
     </row>
-    <row r="25" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3">
         <v>24</v>
       </c>
@@ -1439,7 +1436,7 @@
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
     </row>
-    <row r="26" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3">
         <v>25</v>
       </c>
@@ -1454,7 +1451,7 @@
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
     </row>
-    <row r="27" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
         <v>26</v>
       </c>
@@ -1469,7 +1466,7 @@
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
     </row>
-    <row r="28" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
         <v>27</v>
       </c>
@@ -1484,7 +1481,7 @@
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
     </row>
-    <row r="29" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A29" s="3">
         <v>28</v>
       </c>
@@ -1499,7 +1496,7 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="3">
         <v>29</v>
       </c>
@@ -1514,7 +1511,7 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="1:7" ht="72.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3">
         <v>30</v>
       </c>
@@ -1529,7 +1526,7 @@
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
     </row>
-    <row r="32" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
         <v>31</v>
       </c>
@@ -1544,7 +1541,7 @@
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
     </row>
-    <row r="33" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
         <v>32</v>
       </c>
@@ -1559,7 +1556,7 @@
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
     </row>
-    <row r="34" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3">
         <v>33</v>
       </c>
@@ -1574,7 +1571,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
     </row>
-    <row r="35" spans="1:7" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3">
         <v>34</v>
       </c>
@@ -1589,7 +1586,7 @@
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
     </row>
-    <row r="36" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
         <v>35</v>
       </c>
@@ -1604,7 +1601,7 @@
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
     </row>
-    <row r="37" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
         <v>36</v>
       </c>
@@ -1619,7 +1616,7 @@
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
     </row>
-    <row r="38" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
         <v>37</v>
       </c>
@@ -1634,7 +1631,7 @@
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
     </row>
-    <row r="39" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1703,7 +1700,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -1749,7 +1746,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -1772,7 +1769,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -1795,7 +1792,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -1818,7 +1815,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -1841,7 +1838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="54" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>

--- a/data/araclar.xlsx
+++ b/data/araclar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahip\Documents\olcme_araclari_rehberi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4801459D-72D9-4ECE-AB65-593E29C75F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60947F6-D5CA-4A56-B7E4-2C7DA7B7A8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -220,27 +220,6 @@
 *c) Allah’ın (cc) varlığı ve birliğiyle ilgili bir konuyu seçtiği akli veya naklî delile dayandırarak
 değerlendirir.
 *ç) İlişki kurduğu akli veya naklî delile ilgili konuda amaca uygun şekilde yer verir.</t>
-  </si>
-  <si>
-    <t>Anlam çözümleme tablosu</t>
-  </si>
-  <si>
-    <t>Anlamsal çağrışım haritası</t>
-  </si>
-  <si>
-    <t>Bağlam temelli sorular</t>
-  </si>
-  <si>
-    <t>Balık kılçığı</t>
-  </si>
-  <si>
-    <t>Bilgi görseli</t>
-  </si>
-  <si>
-    <t>Bilgi haritası</t>
-  </si>
-  <si>
-    <t>Boşluk doldurma soruları</t>
   </si>
   <si>
     <t>Bulmacalar</t>
@@ -468,12 +447,6 @@
 DAB4.4. Dinî Konularda Analitik Düşünme</t>
   </si>
   <si>
-    <t>DKAB.9.1.4. Rum suresinin 17-27. ayetlerinin mesajlarını anlamada temel kaynakları
-kullanabilme
-*a) Rum suresinin 17-27. ayetlerinin mesajlarını anlamada Kur’an-ı Kerim meallerine başvurur.
-*b) Rum suresinin 17-27. ayetlerinin mesajlarını anlamada hadis kaynaklarına başvurur.</t>
-  </si>
-  <si>
     <t>DKAB.9.2.2. İslam’ın iman esaslarını ayet ve hadisler bağlamında özetleyebilme
 *a) Ayet ve hadislerden hareketle İslam’ın iman esaslarına ilişkin çözümleme yapar.</t>
   </si>
@@ -564,6 +537,32 @@
   <si>
     <t>SYR.10.3.2. Hz. Peygamber’in farklı inanç gruplarıyla ilişkilerini değerlendirebilme
 *ç) Hz. Peygamber’in farklı inanç gruplarıyla ilişkilerine dair yaptığı karşılaştırmalar hakkında yargıda bulunur.</t>
+  </si>
+  <si>
+    <t>DKAB.9.1.4. Rum suresinin 17-27. ayetlerinin mesajlarını anlamada temel kaynakları kullanabilme
+*a) Rum suresinin 17-27. ayetlerinin mesajlarını anlamada Kur’an-ı Kerim meallerine başvurur.
+*b) Rum suresinin 17-27. ayetlerinin mesajlarını anlamada hadis kaynaklarına başvurur.</t>
+  </si>
+  <si>
+    <t>Anlam Çözümleme Tablosu</t>
+  </si>
+  <si>
+    <t>Anlamsal Çağrışım Haritası</t>
+  </si>
+  <si>
+    <t>Bağlam Temelli Sorular</t>
+  </si>
+  <si>
+    <t>Balık Kılçığı Diyagramı</t>
+  </si>
+  <si>
+    <t>Bilgi Görseli</t>
+  </si>
+  <si>
+    <t>Bilgi Haritası</t>
+  </si>
+  <si>
+    <t>Boşluk Doldurma Soruları</t>
   </si>
 </sst>
 </file>
@@ -1069,22 +1068,22 @@
         <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -1095,22 +1094,22 @@
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>44</v>
+        <v>103</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -1121,22 +1120,22 @@
         <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1147,19 +1146,19 @@
         <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -1170,19 +1169,19 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="357.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -1193,22 +1192,22 @@
         <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1219,7 +1218,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1234,7 +1233,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1249,7 +1248,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -1264,7 +1263,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -1279,7 +1278,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1294,7 +1293,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1309,7 +1308,7 @@
         <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1324,7 +1323,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1339,7 +1338,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -1354,7 +1353,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -1369,7 +1368,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1384,7 +1383,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -1399,7 +1398,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1414,7 +1413,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1429,7 +1428,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1444,7 +1443,7 @@
         <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1459,7 +1458,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1474,7 +1473,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -1489,7 +1488,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1504,7 +1503,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1519,7 +1518,7 @@
         <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1534,7 +1533,7 @@
         <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -1549,7 +1548,7 @@
         <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1564,7 +1563,7 @@
         <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -1579,7 +1578,7 @@
         <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -1594,7 +1593,7 @@
         <v>8</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -1609,7 +1608,7 @@
         <v>8</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -1624,7 +1623,7 @@
         <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1734,16 +1733,16 @@
         <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">

--- a/data/araclar.xlsx
+++ b/data/araclar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sahip\Documents\olcme_araclari_rehberi\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E60947F6-D5CA-4A56-B7E4-2C7DA7B7A8AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF5A5C58-6211-47A7-9031-232072F57268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="111">
   <si>
     <t>arac_id</t>
   </si>
@@ -213,13 +213,6 @@
     <t>TDB.1.1.2. İlkeli yaşamanın önemini idrak edebilme
 *a) İlkeli yaşamanın önemiyle ilgili tefekkür sürecini gözden geçirir.
 *b) İlkeli yaşamanın önemiyle ilgili tefekkür sürecine dayalı çıkarım yapar.</t>
-  </si>
-  <si>
-    <t>AKD.11.2.1. Allah’ın (cc) varlığı ve birliğine ilişkin akli ve naklî delilleri kullanabilme
-*b) Allah’ın (cc) varlığı ve birliğine ilişkin topladığı deliller arasında ilişki kurar.
-*c) Allah’ın (cc) varlığı ve birliğiyle ilgili bir konuyu seçtiği akli veya naklî delile dayandırarak
-değerlendirir.
-*ç) İlişki kurduğu akli veya naklî delile ilgili konuda amaca uygun şekilde yer verir.</t>
   </si>
   <si>
     <t>Bulmacalar</t>
@@ -563,6 +556,21 @@
   </si>
   <si>
     <t>Boşluk Doldurma Soruları</t>
+  </si>
+  <si>
+    <t>HMU.11.1.1. Ülkemizdeki din hizmetlerini müşahede edebilme
+*c) Ülkemizdeki din hizmetleri ile ilgili merak ettiği konuları inceler.</t>
+  </si>
+  <si>
+    <t>EBRU.I.4.1. Battal ebruyu özetleyebilme
+*a) Battal ebruya ilişkin çözümleme yapar.
+*b) Türlerine göre battal ebruları sınıflandırır.</t>
+  </si>
+  <si>
+    <t>AKD.11.2.1. Allah’ın (cc) varlığı ve birliğine ilişkin akli ve naklî delilleri kullanabilme
+*b) Allah’ın (cc) varlığı ve birliğine ilişkin topladığı deliller arasında ilişki kurar.
+*c) Allah’ın (cc) varlığı ve birliğiyle ilgili bir konuyu seçtiği akli veya naklî delile dayandırarak değerlendirir.
+*ç) İlişki kurduğu akli veya naklî delile ilgili konuda amaca uygun şekilde yer verir.</t>
   </si>
 </sst>
 </file>
@@ -1005,7 +1013,7 @@
         <v>41</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1068,22 +1076,25 @@
         <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>74</v>
+      <c r="I5" s="4" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="225.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -1094,22 +1105,22 @@
         <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="H6" s="4" t="s">
         <v>78</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -1120,22 +1131,22 @@
         <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>86</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="238.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1146,19 +1157,19 @@
         <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="409.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -1169,19 +1180,19 @@
         <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="357.6" thickBot="1" x14ac:dyDescent="0.35">
@@ -1192,22 +1203,25 @@
         <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="H10" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>100</v>
+      <c r="I10" s="4" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="43.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1218,7 +1232,7 @@
         <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -1233,7 +1247,7 @@
         <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -1248,7 +1262,7 @@
         <v>8</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -1263,7 +1277,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -1278,7 +1292,7 @@
         <v>8</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1293,7 +1307,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1308,7 +1322,7 @@
         <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1323,7 +1337,7 @@
         <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1338,7 +1352,7 @@
         <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -1353,7 +1367,7 @@
         <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -1368,7 +1382,7 @@
         <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1383,7 +1397,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -1398,7 +1412,7 @@
         <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1413,7 +1427,7 @@
         <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1428,7 +1442,7 @@
         <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1443,7 +1457,7 @@
         <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1458,7 +1472,7 @@
         <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1473,7 +1487,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -1488,7 +1502,7 @@
         <v>8</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1503,7 +1517,7 @@
         <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1518,7 +1532,7 @@
         <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1533,7 +1547,7 @@
         <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -1548,7 +1562,7 @@
         <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1563,7 +1577,7 @@
         <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -1578,7 +1592,7 @@
         <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -1593,7 +1607,7 @@
         <v>8</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -1608,7 +1622,7 @@
         <v>8</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -1623,7 +1637,7 @@
         <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1733,16 +1747,16 @@
         <v>16</v>
       </c>
       <c r="D43" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="F43" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
